--- a/ressourcesCDA/ig/StructureDefinition-fr-actor-extension.xlsx
+++ b/ressourcesCDA/ig/StructureDefinition-fr-actor-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:04:45+00:00</t>
+    <t>2026-02-26T08:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
